--- a/data/trans_orig/Q25_A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años desde que dejó de fumar</t>
+          <t>Tiempo medio en años desde que dejó de fumar (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,34; 14,56</t>
+          <t>12,32; 14,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 17,07</t>
+          <t>14,32; 17,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,72; 17,73</t>
+          <t>14,78; 17,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,35; 20,47</t>
+          <t>17,22; 20,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,86; 12,95</t>
+          <t>7,94; 12,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 9,76</t>
+          <t>5,91; 9,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 17,07</t>
+          <t>7,6; 17,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,0; 19,93</t>
+          <t>13,05; 19,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,84; 13,79</t>
+          <t>11,85; 13,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,23; 15,55</t>
+          <t>13,15; 15,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,79; 16,92</t>
+          <t>13,95; 16,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,81; 19,81</t>
+          <t>16,85; 19,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,99</t>
+          <t>7,15; 9,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 9,58</t>
+          <t>7,7; 9,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,72</t>
+          <t>9,55; 11,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 15,63</t>
+          <t>4,63; 15,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,72</t>
+          <t>4,92; 6,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,95</t>
+          <t>6,9; 8,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 9,13</t>
+          <t>6,86; 9,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,11; 12,38</t>
+          <t>10,12; 12,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,88</t>
+          <t>6,48; 7,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 9,04</t>
+          <t>7,62; 9,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 10,4</t>
+          <t>8,81; 10,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,88</t>
+          <t>5,21; 13,92</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,98; 12,74</t>
+          <t>7,89; 12,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,39; 13,46</t>
+          <t>8,49; 13,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 13,83</t>
+          <t>9,7; 13,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 17,94</t>
+          <t>14,08; 17,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,45</t>
+          <t>5,15; 8,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,37</t>
+          <t>5,83; 9,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 12,35</t>
+          <t>8,54; 12,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,02</t>
+          <t>11,98; 15,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 10,35</t>
+          <t>7,24; 10,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 10,84</t>
+          <t>7,78; 10,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 12,45</t>
+          <t>9,73; 12,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,69; 16,63</t>
+          <t>13,85; 16,58</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,55</t>
+          <t>10,16; 11,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,52 +1146,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 13,5</t>
+          <t>11,88; 13,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 16,68</t>
+          <t>5,97; 16,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 7,71</t>
+          <t>5,96; 7,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,49</t>
+          <t>6,97; 8,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 9,96</t>
+          <t>7,97; 10,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 13,65</t>
+          <t>11,58; 13,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 10,24</t>
+          <t>9,11; 10,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,29</t>
+          <t>10,06; 11,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 11,97</t>
+          <t>10,66; 11,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 15,26</t>
+          <t>7,46; 15,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25_A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,89</t>
+          <t>18,81</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,35</t>
+          <t>16,44</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,37</t>
+          <t>18,32</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,32; 14,5</t>
+          <t>12,23; 14,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 17,02</t>
+          <t>14,27; 17,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 17,65</t>
+          <t>14,61; 17,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 20,45</t>
+          <t>17,05; 20,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 12,97</t>
+          <t>8,01; 13,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,96</t>
+          <t>5,68; 9,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 17,29</t>
+          <t>7,53; 17,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,05; 19,83</t>
+          <t>13,42; 19,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,85; 13,9</t>
+          <t>11,93; 13,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,15; 15,68</t>
+          <t>13,29; 15,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,95; 16,83</t>
+          <t>13,85; 16,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,85; 19,75</t>
+          <t>16,91; 19,8</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,23</t>
+          <t>15,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,24</t>
+          <t>11,16</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>13,55</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 9,01</t>
+          <t>7,16; 9,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 9,63</t>
+          <t>7,64; 9,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 11,85</t>
+          <t>9,7; 11,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 15,54</t>
+          <t>13,97; 16,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,77</t>
+          <t>4,83; 6,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 8,85</t>
+          <t>6,87; 8,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 9,08</t>
+          <t>6,92; 8,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,12; 12,52</t>
+          <t>9,93; 12,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 7,95</t>
+          <t>6,47; 7,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 9,05</t>
+          <t>7,61; 9,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 10,39</t>
+          <t>8,79; 10,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 13,92</t>
+          <t>12,49; 14,36</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,93</t>
+          <t>15,88</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,91</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,15</t>
+          <t>15,31</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,46</t>
+          <t>7,74; 12,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 13,13</t>
+          <t>8,4; 13,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,84</t>
+          <t>9,88; 13,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,08; 17,96</t>
+          <t>13,79; 17,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,44</t>
+          <t>5,02; 8,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,21</t>
+          <t>5,9; 9,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 12,24</t>
+          <t>8,6; 12,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,98; 15,95</t>
+          <t>12,42; 16,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,5</t>
+          <t>7,14; 10,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 10,66</t>
+          <t>7,64; 10,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 12,5</t>
+          <t>9,6; 12,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 16,58</t>
+          <t>13,96; 16,86</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,18</t>
+          <t>16,27</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,6</t>
+          <t>12,67</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,3</t>
+          <t>14,99</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 11,62</t>
+          <t>10,16; 11,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,28; 12,97</t>
+          <t>11,25; 12,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,88; 13,56</t>
+          <t>11,9; 13,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 16,65</t>
+          <t>15,33; 17,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,65</t>
+          <t>5,98; 7,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,97; 8,6</t>
+          <t>6,84; 8,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 10,12</t>
+          <t>7,97; 10,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 13,55</t>
+          <t>11,75; 13,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 10,31</t>
+          <t>9,11; 10,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,06; 11,27</t>
+          <t>10,03; 11,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 11,98</t>
+          <t>10,68; 11,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 15,23</t>
+          <t>14,27; 15,63</t>
         </is>
       </c>
     </row>
